--- a/SourceData/Datas/condition.xlsx
+++ b/SourceData/Datas/condition.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1385,6 +1385,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>GreaterEqual</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>完成：{1}</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
